--- a/Дозор_Пеленг/MB_1712/РАСПИНОВКА_1712.xlsx
+++ b/Дозор_Пеленг/MB_1712/РАСПИНОВКА_1712.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20384"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VPL\DOZOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agest\Downloads\Telegram Desktop\Дозор_Пеленг\MB_1712\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8345629C-4439-4C0A-8E18-050C95EC7FF9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="5835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>P0.0</t>
   </si>
@@ -204,12 +205,18 @@
   </si>
   <si>
     <t>-8</t>
+  </si>
+  <si>
+    <t>VINR</t>
+  </si>
+  <si>
+    <t>LED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -261,9 +268,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -279,6 +283,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,14 +566,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -574,74 +581,74 @@
         <v>25</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1" s="11"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>0</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>1</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <v>1</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -649,26 +656,26 @@
         <v>26</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>2</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>2</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>-3.5</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>2</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -676,14 +683,14 @@
         <v>42</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -691,14 +698,14 @@
         <v>43</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="9"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -706,14 +713,14 @@
         <v>44</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F7" s="8"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -721,14 +728,14 @@
         <v>30</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -736,25 +743,25 @@
         <v>31</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="8"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -762,17 +769,17 @@
         <v>33</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="6"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -780,10 +787,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="6"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -791,10 +798,10 @@
         <v>35</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="6"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -802,10 +809,10 @@
         <v>36</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="6"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -816,7 +823,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -827,7 +834,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -838,7 +845,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -849,7 +856,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
@@ -860,14 +867,14 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -878,7 +885,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -889,7 +896,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
@@ -900,7 +907,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -911,7 +918,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>20</v>
       </c>
@@ -922,7 +929,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -933,7 +940,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
@@ -944,7 +951,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -955,42 +962,42 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
